--- a/Data_clean/MCAS/Estados_US/Edos_USA_2020/LOUISIANA_2020.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2020/LOUISIANA_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D677"/>
+  <dimension ref="A1:D671"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Asientos</t>
@@ -408,22 +413,32 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -487,7 +517,7 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="10">
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Candelaria</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -575,10 +625,15 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Hecelchakán</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -645,10 +715,15 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -662,19 +737,29 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Benemérito de las Américas</t>
+          <t>Benemérito De Las Américas</t>
         </is>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -684,10 +769,15 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Catazajá</t>
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Chilón</t>
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -736,10 +841,15 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -749,10 +859,15 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -762,10 +877,15 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -788,10 +913,15 @@
         <v>2</v>
       </c>
       <c r="D31">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Huitiupán</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -814,10 +949,15 @@
         <v>2</v>
       </c>
       <c r="D33">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -840,10 +985,15 @@
         <v>2</v>
       </c>
       <c r="D35">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -879,10 +1039,15 @@
         <v>2</v>
       </c>
       <c r="D38">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Ostuacán</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Pantepec</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Pichucalco</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -957,10 +1147,15 @@
         <v>2</v>
       </c>
       <c r="D44">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Reforma</t>
@@ -974,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -987,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -1000,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -1013,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Tila</t>
@@ -1026,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1039,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -1052,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -1065,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -1074,10 +1309,15 @@
         <v>2</v>
       </c>
       <c r="D53">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -1091,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Villaflores</t>
@@ -1104,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1135,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Bocoyna</t>
@@ -1148,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -1161,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -1174,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1183,10 +1453,15 @@
         <v>2</v>
       </c>
       <c r="D61">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -1200,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Gran Morelos</t>
@@ -1213,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Guachochi</t>
@@ -1222,13 +1507,18 @@
         <v>2</v>
       </c>
       <c r="D64">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Guadalupe y Calvo</t>
+          <t>Guadalupe Y Calvo</t>
         </is>
       </c>
       <c r="C65">
@@ -1239,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C66">
@@ -1252,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -1265,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1278,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Ojinaga</t>
@@ -1287,10 +1597,15 @@
         <v>2</v>
       </c>
       <c r="D69">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Santa Bárbara</t>
@@ -1304,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1335,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -1348,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -1361,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Múzquiz</t>
@@ -1370,10 +1705,15 @@
         <v>2</v>
       </c>
       <c r="D75">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1387,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1400,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Sacramento</t>
@@ -1413,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -1426,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>San Juan de Sabinas</t>
+          <t>San Juan De Sabinas</t>
         </is>
       </c>
       <c r="C80">
@@ -1439,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -1452,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Sierra Mojada</t>
@@ -1465,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1478,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1509,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Villa de Álvarez</t>
+          <t>Villa De Álvarez</t>
         </is>
       </c>
       <c r="C86">
@@ -1522,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1531,13 +1921,13 @@
         <v>2</v>
       </c>
       <c r="D87">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1553,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1566,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1575,10 +1975,15 @@
         <v>2</v>
       </c>
       <c r="D90">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1592,19 +1997,29 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1618,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1631,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1644,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1657,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1670,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1683,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1696,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1709,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1722,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1753,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Cuencamé</t>
@@ -1766,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1779,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1792,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1805,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1818,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Guanaceví</t>
@@ -1831,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1844,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -1857,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nombre de Dios</t>
+          <t>Nombre De Dios</t>
         </is>
       </c>
       <c r="C112">
@@ -1870,19 +2375,29 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Pánuco de Coronado</t>
+          <t>Pánuco De Coronado</t>
         </is>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -1892,10 +2407,15 @@
         <v>2</v>
       </c>
       <c r="D114">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Rodeo</t>
@@ -1909,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -1922,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Súchil</t>
@@ -1931,10 +2461,15 @@
         <v>2</v>
       </c>
       <c r="D117">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Vicente Guerero</t>
@@ -1948,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1963,12 +2503,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C120">
@@ -1979,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C121">
@@ -1992,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -2005,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Amecameca</t>
@@ -2018,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -2031,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Coacalco de Berriozábal</t>
+          <t>Coacalco De Berriozábal</t>
         </is>
       </c>
       <c r="C125">
@@ -2044,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -2057,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C127">
@@ -2070,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Huixquilucan</t>
@@ -2083,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -2096,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -2109,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -2122,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Joquicingo</t>
@@ -2135,19 +2735,29 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C133">
         <v>2</v>
       </c>
       <c r="D133">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -2161,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Nicolás Romero</t>
@@ -2174,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Otzoloapan</t>
@@ -2187,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -2200,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>San Simón de Guerero</t>
+          <t>San Simón De Guerero</t>
         </is>
       </c>
       <c r="C138">
@@ -2213,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Santo Tomás</t>
@@ -2226,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -2239,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -2252,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -2265,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C143">
@@ -2278,9 +2933,14 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C144">
@@ -2291,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2304,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2317,22 +2987,32 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Villa de Allende</t>
+          <t>Villa De Allende</t>
         </is>
       </c>
       <c r="C147">
         <v>2</v>
       </c>
       <c r="D147">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Villa del Carbón</t>
+          <t>Villa Del Carbón</t>
         </is>
       </c>
       <c r="C148">
@@ -2343,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -2356,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2371,7 +3061,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2387,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -2396,10 +3091,15 @@
         <v>2</v>
       </c>
       <c r="D152">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -2413,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C154">
@@ -2426,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C155">
@@ -2439,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -2452,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -2465,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Coroneo</t>
@@ -2474,10 +3199,15 @@
         <v>2</v>
       </c>
       <c r="D158">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -2491,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -2500,13 +3235,18 @@
         <v>2</v>
       </c>
       <c r="D160">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C161">
@@ -2517,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -2530,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -2543,19 +3293,29 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Jaral del Progreso</t>
+          <t>Jaral Del Progreso</t>
         </is>
       </c>
       <c r="C164">
         <v>2</v>
       </c>
       <c r="D164">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -2569,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>León</t>
@@ -2582,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -2591,10 +3361,15 @@
         <v>2</v>
       </c>
       <c r="D167">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -2608,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -2617,10 +3397,15 @@
         <v>2</v>
       </c>
       <c r="D169">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -2630,10 +3415,15 @@
         <v>2</v>
       </c>
       <c r="D170">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -2647,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -2660,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>San Diego de la Unión</t>
+          <t>San Diego De La Unión</t>
         </is>
       </c>
       <c r="C173">
@@ -2673,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -2686,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -2699,22 +3509,32 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C176">
         <v>20</v>
       </c>
       <c r="D176">
-        <v>0.009708737864077669</v>
+        <v>0.009708737864077667</v>
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C177">
@@ -2725,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -2738,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -2751,9 +3581,14 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C180">
@@ -2764,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -2777,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -2790,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Xichú</t>
@@ -2803,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -2841,7 +3696,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C186">
@@ -2852,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -2865,9 +3725,14 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C188">
@@ -2878,9 +3743,14 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Alcozauca de Guerero</t>
+          <t>Alcozauca De Guerero</t>
         </is>
       </c>
       <c r="C189">
@@ -2891,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Apaxtla</t>
@@ -2904,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -2917,9 +3797,14 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Atenango del Río</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C192">
@@ -2930,9 +3815,14 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C193">
@@ -2943,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -2952,13 +3847,18 @@
         <v>2</v>
       </c>
       <c r="D194">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Buenavista de Cuéllar</t>
+          <t>Buenavista De Cuéllar</t>
         </is>
       </c>
       <c r="C195">
@@ -2969,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C196">
@@ -2982,9 +3887,14 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C197">
@@ -2995,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Copala</t>
@@ -3008,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -3021,9 +3941,14 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C200">
@@ -3034,9 +3959,14 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C201">
@@ -3047,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Cualác</t>
@@ -3060,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Cuetzala del Progreso</t>
+          <t>Cuetzala Del Progreso</t>
         </is>
       </c>
       <c r="C203">
@@ -3073,19 +4013,29 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C204">
         <v>2</v>
       </c>
       <c r="D204">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -3099,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -3112,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>General Canuto A. Neri</t>
@@ -3125,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -3138,9 +4103,14 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C209">
@@ -3151,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C210">
@@ -3164,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -3173,10 +4153,15 @@
         <v>2</v>
       </c>
       <c r="D211">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -3186,10 +4171,15 @@
         <v>2</v>
       </c>
       <c r="D212">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -3203,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -3212,10 +4207,15 @@
         <v>2</v>
       </c>
       <c r="D214">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -3229,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -3242,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C217">
@@ -3255,19 +4265,29 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C218">
         <v>2</v>
       </c>
       <c r="D218">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -3281,9 +4301,14 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C220">
@@ -3294,9 +4319,14 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Tixtla de Guerero</t>
+          <t>Tixtla De Guerero</t>
         </is>
       </c>
       <c r="C221">
@@ -3307,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -3320,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C223">
@@ -3333,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -3346,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Zapotitlán Tablas</t>
@@ -3359,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -3372,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3392,7 +4452,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C228">
@@ -3403,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Cardonal</t>
@@ -3416,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -3429,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -3438,10 +4513,15 @@
         <v>2</v>
       </c>
       <c r="D231">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -3455,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -3468,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -3481,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Jacala de Ledezma</t>
+          <t>Jacala De Ledezma</t>
         </is>
       </c>
       <c r="C235">
@@ -3494,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>La Misión</t>
@@ -3507,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -3520,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Mixquiahuala de Juárez</t>
+          <t>Mixquiahuala De Juárez</t>
         </is>
       </c>
       <c r="C238">
@@ -3533,19 +4643,29 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C239">
         <v>2</v>
       </c>
       <c r="D239">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Pisaflores</t>
@@ -3559,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>San Bartolo Tutotepec</t>
@@ -3572,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>San Felipe Orizatlán</t>
@@ -3585,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Singuilucan</t>
@@ -3598,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -3611,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -3620,13 +4765,18 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Tenango de Doria</t>
+          <t>Tenango De Doria</t>
         </is>
       </c>
       <c r="C246">
@@ -3637,9 +4787,14 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerero</t>
+          <t>Tepehuacán De Guerero</t>
         </is>
       </c>
       <c r="C247">
@@ -3650,9 +4805,14 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Tepeji del Río de Ocampo</t>
+          <t>Tepeji Del Río De Ocampo</t>
         </is>
       </c>
       <c r="C248">
@@ -3663,19 +4823,29 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Tezontepec de Aldama</t>
+          <t>Tezontepec De Aldama</t>
         </is>
       </c>
       <c r="C249">
         <v>2</v>
       </c>
       <c r="D249">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Tianguistengo</t>
@@ -3685,10 +4855,15 @@
         <v>2</v>
       </c>
       <c r="D250">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Tlahuelilpan</t>
@@ -3702,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -3715,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -3728,9 +4913,14 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C254">
@@ -3741,9 +4931,14 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Zacualtipán de Ángeles</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C255">
@@ -3754,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -3767,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3798,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Ameca</t>
@@ -3811,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Arandas</t>
@@ -3820,10 +5035,15 @@
         <v>2</v>
       </c>
       <c r="D260">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Atenguillo</t>
@@ -3837,9 +5057,14 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C262">
@@ -3850,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Colotlán</t>
@@ -3863,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -3876,9 +5111,14 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C265">
@@ -3889,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -3902,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Hostotipaquillo</t>
@@ -3915,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -3928,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -3941,19 +5201,29 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C270">
         <v>2</v>
       </c>
       <c r="D270">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -3967,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Mazamitla</t>
@@ -3976,10 +5251,15 @@
         <v>2</v>
       </c>
       <c r="D272">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -3989,10 +5269,15 @@
         <v>2</v>
       </c>
       <c r="D273">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Pihuamo</t>
@@ -4006,9 +5291,14 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C275">
@@ -4019,9 +5309,14 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Talpa de Allende</t>
+          <t>Talpa De Allende</t>
         </is>
       </c>
       <c r="C276">
@@ -4032,9 +5327,14 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C277">
@@ -4045,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -4054,10 +5359,15 @@
         <v>2</v>
       </c>
       <c r="D278">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Tecolotlán</t>
@@ -4071,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -4084,22 +5399,32 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C281">
         <v>2</v>
       </c>
       <c r="D281">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C282">
@@ -4110,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -4123,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -4136,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -4149,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -4162,9 +5507,14 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Zapotitlán de Vadillo</t>
+          <t>Zapotitlán De Vadillo</t>
         </is>
       </c>
       <c r="C287">
@@ -4175,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4206,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -4219,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Buenavista</t>
@@ -4232,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -4245,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -4258,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Cotija</t>
@@ -4271,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Cuitzeo</t>
@@ -4284,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Epitacio Huerta</t>
@@ -4293,10 +5683,15 @@
         <v>2</v>
       </c>
       <c r="D296">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -4310,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Huandacareo</t>
@@ -4323,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -4336,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Indaparapeo</t>
@@ -4345,10 +5755,15 @@
         <v>2</v>
       </c>
       <c r="D300">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Irimbo</t>
@@ -4362,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -4375,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -4384,10 +5809,15 @@
         <v>2</v>
       </c>
       <c r="D303">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -4401,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -4414,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Madero</t>
@@ -4423,10 +5863,15 @@
         <v>2</v>
       </c>
       <c r="D306">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -4440,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -4449,10 +5899,15 @@
         <v>2</v>
       </c>
       <c r="D308">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -4466,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -4479,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -4492,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -4505,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -4518,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Santa Ana Maya</t>
@@ -4531,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Senguio</t>
@@ -4540,10 +6025,15 @@
         <v>2</v>
       </c>
       <c r="D315">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Susupuato</t>
@@ -4553,10 +6043,15 @@
         <v>2</v>
       </c>
       <c r="D316">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -4570,9 +6065,14 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C318">
@@ -4583,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Tocumbo</t>
@@ -4596,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Tumbiscatío</t>
@@ -4605,10 +6115,15 @@
         <v>2</v>
       </c>
       <c r="D320">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -4622,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -4635,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Tzitzio</t>
@@ -4644,10 +6169,15 @@
         <v>2</v>
       </c>
       <c r="D323">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -4661,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -4674,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -4687,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -4700,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4727,10 +6277,15 @@
         <v>2</v>
       </c>
       <c r="D329">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Ayala</t>
@@ -4744,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -4757,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -4770,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Jantetelco</t>
@@ -4783,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Jiutepec</t>
@@ -4796,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Temoac</t>
@@ -4809,9 +6389,14 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C336">
@@ -4822,9 +6407,14 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C337">
@@ -4835,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Xochitepec</t>
@@ -4844,10 +6439,15 @@
         <v>2</v>
       </c>
       <c r="D338">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4875,10 +6475,15 @@
         <v>2</v>
       </c>
       <c r="D340">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Jala</t>
@@ -4892,6 +6497,11 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -4905,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -4918,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>San Pedro Lagunillas</t>
@@ -4931,9 +6551,14 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C345">
@@ -4944,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -4953,10 +6583,15 @@
         <v>2</v>
       </c>
       <c r="D346">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -4966,10 +6601,15 @@
         <v>2</v>
       </c>
       <c r="D347">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5001,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Cadereyta Jiménez</t>
@@ -5010,10 +6655,15 @@
         <v>2</v>
       </c>
       <c r="D350">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Cerralvo</t>
@@ -5023,10 +6673,15 @@
         <v>2</v>
       </c>
       <c r="D351">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Doctor Arroyo</t>
@@ -5040,6 +6695,11 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>Galeana</t>
@@ -5053,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>General Bravo</t>
@@ -5066,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -5079,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -5092,9 +6767,14 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MonteMorelos</t>
+          <t>Montemorelos</t>
         </is>
       </c>
       <c r="C357">
@@ -5105,6 +6785,11 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -5118,9 +6803,14 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C359">
@@ -5131,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>San Pedro Garza García</t>
@@ -5140,10 +6835,15 @@
         <v>2</v>
       </c>
       <c r="D360">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5164,7 +6864,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C362">
@@ -5175,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Candelaria Loxicha</t>
@@ -5188,9 +6893,14 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Constancia del Rosario</t>
+          <t>Constancia Del Rosario</t>
         </is>
       </c>
       <c r="C364">
@@ -5201,9 +6911,14 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C365">
@@ -5214,22 +6929,32 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C366">
         <v>2</v>
       </c>
       <c r="D366">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C367">
@@ -5240,6 +6965,11 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -5253,9 +6983,14 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Mazatlán Villa de Flores</t>
+          <t>Mazatlán Villa De Flores</t>
         </is>
       </c>
       <c r="C369">
@@ -5266,9 +7001,14 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C370">
@@ -5279,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Monjas</t>
@@ -5292,9 +7037,14 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C372">
@@ -5305,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C373">
@@ -5318,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -5331,6 +7091,11 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -5344,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>San Felipe Usila</t>
@@ -5357,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>San Francisco Ixhuatán</t>
@@ -5366,10 +7141,15 @@
         <v>2</v>
       </c>
       <c r="D377">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>San Jerónimo Taviche</t>
@@ -5383,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -5392,10 +7177,15 @@
         <v>2</v>
       </c>
       <c r="D379">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -5409,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>San Juan Guichicovi</t>
@@ -5422,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>San Juan Mazatlán</t>
@@ -5431,10 +7231,15 @@
         <v>2</v>
       </c>
       <c r="D382">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>San Juan Quiahije</t>
@@ -5448,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>San Lorenzo</t>
@@ -5461,6 +7271,11 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>San Lucas Ojitlán</t>
@@ -5470,10 +7285,15 @@
         <v>2</v>
       </c>
       <c r="D385">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>San Miguel Chicahua</t>
@@ -5487,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>San Miguel Panixtlahuaca</t>
@@ -5496,10 +7321,15 @@
         <v>2</v>
       </c>
       <c r="D387">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -5513,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>San Pablo Huixtepec</t>
@@ -5526,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>San Pedro Tapanatepec</t>
@@ -5539,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Santa María Chimalapa</t>
@@ -5552,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -5565,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>Santa María Temaxcaltepec</t>
@@ -5574,10 +7429,15 @@
         <v>2</v>
       </c>
       <c r="D393">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Santa María Tlahuitoltepec</t>
@@ -5591,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>Santa María Totolapilla</t>
@@ -5600,10 +7465,15 @@
         <v>2</v>
       </c>
       <c r="D395">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Santiago Chazumba</t>
@@ -5613,10 +7483,15 @@
         <v>2</v>
       </c>
       <c r="D396">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -5626,10 +7501,15 @@
         <v>2</v>
       </c>
       <c r="D397">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -5639,10 +7519,15 @@
         <v>2</v>
       </c>
       <c r="D398">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>Santiago Yaitepec</t>
@@ -5656,9 +7541,14 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Santo Domingo de Morelos</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C400">
@@ -5669,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -5682,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -5695,9 +7595,14 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Teotitlán de Flores Magón</t>
+          <t>Teotitlán De Flores Magón</t>
         </is>
       </c>
       <c r="C403">
@@ -5708,9 +7613,14 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Totontepec Villa de Morelos</t>
+          <t>Totontepec Villa De Morelos</t>
         </is>
       </c>
       <c r="C404">
@@ -5721,9 +7631,14 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Villa de Etla</t>
+          <t>Villa De Etla</t>
         </is>
       </c>
       <c r="C405">
@@ -5734,22 +7649,32 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C406">
         <v>2</v>
       </c>
       <c r="D406">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C407">
@@ -5760,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5791,6 +7721,11 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Acatzingo</t>
@@ -5804,6 +7739,11 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>Aquixtla</t>
@@ -5813,10 +7753,15 @@
         <v>2</v>
       </c>
       <c r="D411">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Atempan</t>
@@ -5826,10 +7771,15 @@
         <v>2</v>
       </c>
       <c r="D412">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -5843,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>Calpan</t>
@@ -5856,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -5869,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -5882,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -5895,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Coxcatlán</t>
@@ -5908,9 +7883,14 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Cuetzalan del Progreso</t>
+          <t>Cuetzalan Del Progreso</t>
         </is>
       </c>
       <c r="C419">
@@ -5921,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -5934,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -5947,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -5956,23 +7951,33 @@
         <v>2</v>
       </c>
       <c r="D422">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C423">
         <v>2</v>
       </c>
       <c r="D423">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -5986,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Hueyapan</t>
@@ -5999,6 +8009,11 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -6008,10 +8023,15 @@
         <v>2</v>
       </c>
       <c r="D426">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Jopala</t>
@@ -6025,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Juan C. Bonilla</t>
@@ -6038,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -6051,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Oriental</t>
@@ -6064,9 +8099,14 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C431">
@@ -6077,6 +8117,11 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>Pantepec</t>
@@ -6086,10 +8131,15 @@
         <v>2</v>
       </c>
       <c r="D432">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -6103,6 +8153,11 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -6116,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>San Felipe Tepatlán</t>
@@ -6129,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>San Miguel Xoxtla</t>
@@ -6142,9 +8207,14 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>San Salvador el Seco</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C437">
@@ -6155,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -6164,13 +8239,18 @@
         <v>2</v>
       </c>
       <c r="D438">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Tepatlaxco de Hidalgo</t>
+          <t>Tepatlaxco De Hidalgo</t>
         </is>
       </c>
       <c r="C439">
@@ -6181,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -6194,9 +8279,14 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C441">
@@ -6207,9 +8297,14 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C442">
@@ -6220,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -6233,19 +8333,29 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Tuzamapan de Galeana</t>
+          <t>Tuzamapan De Galeana</t>
         </is>
       </c>
       <c r="C444">
         <v>2</v>
       </c>
       <c r="D444">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -6259,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -6268,10 +8383,15 @@
         <v>2</v>
       </c>
       <c r="D446">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>Yaonáhuac</t>
@@ -6285,6 +8405,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -6294,10 +8419,15 @@
         <v>2</v>
       </c>
       <c r="D448">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Zacapala</t>
@@ -6311,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -6324,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -6333,10 +8473,15 @@
         <v>2</v>
       </c>
       <c r="D451">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -6350,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Zihuateutla</t>
@@ -6359,10 +8509,15 @@
         <v>2</v>
       </c>
       <c r="D453">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6383,7 +8538,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C455">
@@ -6394,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Arroyo Seco</t>
@@ -6407,9 +8567,14 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C457">
@@ -6420,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Colón</t>
@@ -6433,6 +8603,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Corregidora</t>
@@ -6442,10 +8617,15 @@
         <v>2</v>
       </c>
       <c r="D459">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Ezequiel Montes</t>
@@ -6459,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Huimilpan</t>
@@ -6472,9 +8657,14 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C462">
@@ -6485,19 +8675,29 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C463">
         <v>2</v>
       </c>
       <c r="D463">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Pedro Escobedo</t>
@@ -6511,19 +8711,29 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C465">
         <v>2</v>
       </c>
       <c r="D465">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -6537,9 +8747,14 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C467">
@@ -6550,6 +8765,11 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Tequisquiapan</t>
@@ -6563,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6590,10 +8815,15 @@
         <v>2</v>
       </c>
       <c r="D470">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>Isla Mujeres</t>
@@ -6607,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Othón P. Blanco</t>
@@ -6620,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6647,10 +8887,15 @@
         <v>2</v>
       </c>
       <c r="D474">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Alaquines</t>
@@ -6664,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Aquismón</t>
@@ -6673,10 +8923,15 @@
         <v>2</v>
       </c>
       <c r="D476">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -6686,10 +8941,15 @@
         <v>2</v>
       </c>
       <c r="D477">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Cerritos</t>
@@ -6703,9 +8963,14 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Cerro de San Pedro</t>
+          <t>Cerro De San Pedro</t>
         </is>
       </c>
       <c r="C479">
@@ -6716,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Charcas</t>
@@ -6729,9 +8999,14 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C481">
@@ -6742,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -6755,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -6768,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>Coxcatlán</t>
@@ -6781,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Ebano</t>
@@ -6794,6 +9089,11 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Guadalcázar</t>
@@ -6807,6 +9107,11 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
           <t>Huehuetlán</t>
@@ -6816,10 +9121,15 @@
         <v>2</v>
       </c>
       <c r="D487">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -6833,6 +9143,11 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -6846,9 +9161,14 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C490">
@@ -6859,6 +9179,11 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -6872,6 +9197,11 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -6885,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -6898,6 +9233,11 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
           <t>San Martín Chalchicuautla</t>
@@ -6911,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>San Nicolás Tolentino</t>
@@ -6920,10 +9265,15 @@
         <v>2</v>
       </c>
       <c r="D495">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>San Vicente Tancuayalab</t>
@@ -6933,10 +9283,15 @@
         <v>2</v>
       </c>
       <c r="D496">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Santa Catarina</t>
@@ -6950,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -6963,6 +9323,11 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -6976,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -6989,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Tamuín</t>
@@ -6998,10 +9373,15 @@
         <v>2</v>
       </c>
       <c r="D501">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
           <t>Tanlajás</t>
@@ -7015,19 +9395,29 @@
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Tanquián de Escobedo</t>
+          <t>Tanquián De Escobedo</t>
         </is>
       </c>
       <c r="C503">
         <v>2</v>
       </c>
       <c r="D503">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Tierra Nueva</t>
@@ -7041,9 +9431,14 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Villa de Arista</t>
+          <t>Villa De Arista</t>
         </is>
       </c>
       <c r="C505">
@@ -7054,9 +9449,14 @@
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Villa de Arriaga</t>
+          <t>Villa De Arriaga</t>
         </is>
       </c>
       <c r="C506">
@@ -7067,9 +9467,14 @@
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Villa de Guadalupe</t>
+          <t>Villa De Guadalupe</t>
         </is>
       </c>
       <c r="C507">
@@ -7080,9 +9485,14 @@
       </c>
     </row>
     <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C508">
@@ -7093,9 +9503,14 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Villa de Reyes</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C509">
@@ -7106,6 +9521,11 @@
       </c>
     </row>
     <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B510" t="inlineStr">
         <is>
           <t>Villa Juárez</t>
@@ -7119,6 +9539,11 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -7132,6 +9557,11 @@
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7163,6 +9593,11 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -7176,6 +9611,11 @@
       </c>
     </row>
     <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -7189,6 +9629,11 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -7198,10 +9643,15 @@
         <v>2</v>
       </c>
       <c r="D516">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -7215,6 +9665,11 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
           <t>Sinaloa</t>
@@ -7228,6 +9683,11 @@
       </c>
     </row>
     <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B519" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7259,6 +9719,11 @@
       </c>
     </row>
     <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
           <t>Etchojoa</t>
@@ -7272,6 +9737,11 @@
       </c>
     </row>
     <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -7285,6 +9755,11 @@
       </c>
     </row>
     <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B523" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -7294,10 +9769,15 @@
         <v>2</v>
       </c>
       <c r="D523">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B524" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -7311,6 +9791,11 @@
       </c>
     </row>
     <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7342,6 +9827,11 @@
       </c>
     </row>
     <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -7355,6 +9845,11 @@
       </c>
     </row>
     <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
           <t>Centla</t>
@@ -7368,6 +9863,11 @@
       </c>
     </row>
     <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -7381,6 +9881,11 @@
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B530" t="inlineStr">
         <is>
           <t>Comalcalco</t>
@@ -7394,6 +9899,11 @@
       </c>
     </row>
     <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr">
         <is>
           <t>Cunduacán</t>
@@ -7407,6 +9917,11 @@
       </c>
     </row>
     <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B532" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -7420,6 +9935,11 @@
       </c>
     </row>
     <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B533" t="inlineStr">
         <is>
           <t>Jonuta</t>
@@ -7433,6 +9953,11 @@
       </c>
     </row>
     <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B534" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -7442,10 +9967,15 @@
         <v>2</v>
       </c>
       <c r="D534">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B535" t="inlineStr">
         <is>
           <t>Nacajuca</t>
@@ -7459,6 +9989,11 @@
       </c>
     </row>
     <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B536" t="inlineStr">
         <is>
           <t>Paraíso</t>
@@ -7468,10 +10003,15 @@
         <v>2</v>
       </c>
       <c r="D536">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr">
         <is>
           <t>Tenosique</t>
@@ -7481,10 +10021,15 @@
         <v>20</v>
       </c>
       <c r="D537">
-        <v>0.009708737864077669</v>
+        <v>0.009708737864077667</v>
       </c>
     </row>
     <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B538" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7516,6 +10061,11 @@
       </c>
     </row>
     <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B540" t="inlineStr">
         <is>
           <t>Altamira</t>
@@ -7529,6 +10079,11 @@
       </c>
     </row>
     <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B541" t="inlineStr">
         <is>
           <t>Bustamante</t>
@@ -7542,6 +10097,11 @@
       </c>
     </row>
     <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B542" t="inlineStr">
         <is>
           <t>Ciudad Madero</t>
@@ -7555,6 +10115,11 @@
       </c>
     </row>
     <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B543" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -7568,6 +10133,11 @@
       </c>
     </row>
     <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B544" t="inlineStr">
         <is>
           <t>González</t>
@@ -7581,6 +10151,11 @@
       </c>
     </row>
     <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -7590,10 +10165,15 @@
         <v>2</v>
       </c>
       <c r="D545">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B546" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -7603,10 +10183,15 @@
         <v>2</v>
       </c>
       <c r="D546">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B547" t="inlineStr">
         <is>
           <t>Llera</t>
@@ -7620,6 +10205,11 @@
       </c>
     </row>
     <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B548" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -7633,6 +10223,11 @@
       </c>
     </row>
     <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr">
         <is>
           <t>Méndez</t>
@@ -7646,6 +10241,11 @@
       </c>
     </row>
     <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B550" t="inlineStr">
         <is>
           <t>Mier</t>
@@ -7659,6 +10259,11 @@
       </c>
     </row>
     <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr">
         <is>
           <t>Miguel Alemán</t>
@@ -7672,6 +10277,11 @@
       </c>
     </row>
     <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -7685,6 +10295,11 @@
       </c>
     </row>
     <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B553" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -7698,6 +10313,11 @@
       </c>
     </row>
     <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B554" t="inlineStr">
         <is>
           <t>Padilla</t>
@@ -7707,10 +10327,15 @@
         <v>2</v>
       </c>
       <c r="D554">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B555" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -7724,6 +10349,11 @@
       </c>
     </row>
     <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B556" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -7737,6 +10367,11 @@
       </c>
     </row>
     <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B557" t="inlineStr">
         <is>
           <t>San Fernando</t>
@@ -7746,13 +10381,18 @@
         <v>2</v>
       </c>
       <c r="D557">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Soto la Marina</t>
+          <t>Soto La Marina</t>
         </is>
       </c>
       <c r="C558">
@@ -7763,6 +10403,11 @@
       </c>
     </row>
     <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -7776,6 +10421,11 @@
       </c>
     </row>
     <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B560" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -7789,6 +10439,11 @@
       </c>
     </row>
     <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B561" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -7802,6 +10457,11 @@
       </c>
     </row>
     <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B562" t="inlineStr">
         <is>
           <t>Xicoténcatl</t>
@@ -7815,6 +10475,11 @@
       </c>
     </row>
     <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7846,6 +10511,11 @@
       </c>
     </row>
     <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -7859,6 +10529,11 @@
       </c>
     </row>
     <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B566" t="inlineStr">
         <is>
           <t>Teolocholco</t>
@@ -7872,6 +10547,11 @@
       </c>
     </row>
     <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B567" t="inlineStr">
         <is>
           <t>Tetlatlahuca</t>
@@ -7885,6 +10565,11 @@
       </c>
     </row>
     <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B568" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -7894,10 +10579,15 @@
         <v>2</v>
       </c>
       <c r="D568">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B569" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7929,6 +10619,11 @@
       </c>
     </row>
     <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B571" t="inlineStr">
         <is>
           <t>Acayucan</t>
@@ -7942,6 +10637,11 @@
       </c>
     </row>
     <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B572" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -7955,6 +10655,11 @@
       </c>
     </row>
     <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B573" t="inlineStr">
         <is>
           <t>Acula</t>
@@ -7968,6 +10673,11 @@
       </c>
     </row>
     <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B574" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -7981,6 +10691,11 @@
       </c>
     </row>
     <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B575" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -7994,6 +10709,11 @@
       </c>
     </row>
     <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B576" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -8003,13 +10723,18 @@
         <v>2</v>
       </c>
       <c r="D576">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Boca del Río</t>
+          <t>Boca Del Río</t>
         </is>
       </c>
       <c r="C577">
@@ -8020,6 +10745,11 @@
       </c>
     </row>
     <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B578" t="inlineStr">
         <is>
           <t>Carrillo Puerto</t>
@@ -8033,6 +10763,11 @@
       </c>
     </row>
     <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B579" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -8042,10 +10777,15 @@
         <v>2</v>
       </c>
       <c r="D579">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B580" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -8055,10 +10795,15 @@
         <v>2</v>
       </c>
       <c r="D580">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B581" t="inlineStr">
         <is>
           <t>Chicontepec</t>
@@ -8072,6 +10817,11 @@
       </c>
     </row>
     <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B582" t="inlineStr">
         <is>
           <t>Coatepec</t>
@@ -8085,6 +10835,11 @@
       </c>
     </row>
     <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B583" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -8094,10 +10849,15 @@
         <v>2</v>
       </c>
       <c r="D583">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B584" t="inlineStr">
         <is>
           <t>Comapa</t>
@@ -8111,6 +10871,11 @@
       </c>
     </row>
     <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B585" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -8124,19 +10889,29 @@
       </c>
     </row>
     <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C586">
         <v>2</v>
       </c>
       <c r="D586">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B587" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -8150,6 +10925,11 @@
       </c>
     </row>
     <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B588" t="inlineStr">
         <is>
           <t>Espinal</t>
@@ -8163,6 +10943,11 @@
       </c>
     </row>
     <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B589" t="inlineStr">
         <is>
           <t>Fortín</t>
@@ -8172,10 +10957,15 @@
         <v>2</v>
       </c>
       <c r="D589">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B590" t="inlineStr">
         <is>
           <t>Gutiérrez Zamora</t>
@@ -8185,10 +10975,15 @@
         <v>2</v>
       </c>
       <c r="D590">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B591" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -8198,10 +10993,15 @@
         <v>2</v>
       </c>
       <c r="D591">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B592" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -8215,9 +11015,14 @@
       </c>
     </row>
     <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C593">
@@ -8228,9 +11033,14 @@
       </c>
     </row>
     <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C594">
@@ -8241,6 +11051,11 @@
       </c>
     </row>
     <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B595" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -8254,9 +11069,14 @@
       </c>
     </row>
     <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Ixhuatlán del Café</t>
+          <t>Ixhuatlán Del Café</t>
         </is>
       </c>
       <c r="C596">
@@ -8267,6 +11087,11 @@
       </c>
     </row>
     <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B597" t="inlineStr">
         <is>
           <t>Ixtaczoquitlán</t>
@@ -8276,10 +11101,15 @@
         <v>2</v>
       </c>
       <c r="D597">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B598" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -8293,6 +11123,11 @@
       </c>
     </row>
     <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B599" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -8306,9 +11141,14 @@
       </c>
     </row>
     <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Juchique de Ferrer</t>
+          <t>Juchique De Ferrer</t>
         </is>
       </c>
       <c r="C600">
@@ -8319,6 +11159,11 @@
       </c>
     </row>
     <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B601" t="inlineStr">
         <is>
           <t>La Antigua</t>
@@ -8332,6 +11177,11 @@
       </c>
     </row>
     <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B602" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -8341,10 +11191,15 @@
         <v>2</v>
       </c>
       <c r="D602">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B603" t="inlineStr">
         <is>
           <t>Maltrata</t>
@@ -8358,6 +11213,11 @@
       </c>
     </row>
     <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B604" t="inlineStr">
         <is>
           <t>Manlio Fabio Altamirano</t>
@@ -8371,9 +11231,14 @@
       </c>
     </row>
     <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C605">
@@ -8384,19 +11249,29 @@
       </c>
     </row>
     <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Medellín de Bravo</t>
+          <t>Medellín De Bravo</t>
         </is>
       </c>
       <c r="C606">
         <v>2</v>
       </c>
       <c r="D606">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B607" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -8410,6 +11285,11 @@
       </c>
     </row>
     <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B608" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -8423,6 +11303,11 @@
       </c>
     </row>
     <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B609" t="inlineStr">
         <is>
           <t>Moloacán</t>
@@ -8436,6 +11321,11 @@
       </c>
     </row>
     <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B610" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -8445,10 +11335,15 @@
         <v>2</v>
       </c>
       <c r="D610">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B611" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -8462,6 +11357,11 @@
       </c>
     </row>
     <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B612" t="inlineStr">
         <is>
           <t>Otatitlán</t>
@@ -8475,6 +11375,11 @@
       </c>
     </row>
     <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B613" t="inlineStr">
         <is>
           <t>Oteapan</t>
@@ -8488,19 +11393,29 @@
       </c>
     </row>
     <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Ozuluama de Mascareñas</t>
+          <t>Ozuluama De Mascareñas</t>
         </is>
       </c>
       <c r="C614">
         <v>2</v>
       </c>
       <c r="D614">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B615" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -8514,6 +11429,11 @@
       </c>
     </row>
     <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B616" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -8527,9 +11447,14 @@
       </c>
     </row>
     <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C617">
@@ -8540,6 +11465,11 @@
       </c>
     </row>
     <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B618" t="inlineStr">
         <is>
           <t>Perote</t>
@@ -8553,6 +11483,11 @@
       </c>
     </row>
     <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B619" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -8566,9 +11501,14 @@
       </c>
     </row>
     <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C620">
@@ -8579,6 +11519,11 @@
       </c>
     </row>
     <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B621" t="inlineStr">
         <is>
           <t>Pueblo Viejo</t>
@@ -8592,6 +11537,11 @@
       </c>
     </row>
     <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B622" t="inlineStr">
         <is>
           <t>Río Blanco</t>
@@ -8601,10 +11551,15 @@
         <v>2</v>
       </c>
       <c r="D622">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B623" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -8618,6 +11573,11 @@
       </c>
     </row>
     <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B624" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -8631,6 +11591,11 @@
       </c>
     </row>
     <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B625" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -8644,6 +11609,11 @@
       </c>
     </row>
     <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B626" t="inlineStr">
         <is>
           <t>Soconusco</t>
@@ -8657,9 +11627,14 @@
       </c>
     </row>
     <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C627">
@@ -8670,6 +11645,11 @@
       </c>
     </row>
     <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B628" t="inlineStr">
         <is>
           <t>Tampico Alto</t>
@@ -8683,6 +11663,11 @@
       </c>
     </row>
     <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B629" t="inlineStr">
         <is>
           <t>Tantoyuca</t>
@@ -8696,6 +11681,11 @@
       </c>
     </row>
     <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B630" t="inlineStr">
         <is>
           <t>Tecolutla</t>
@@ -8709,6 +11699,11 @@
       </c>
     </row>
     <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B631" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -8722,6 +11717,11 @@
       </c>
     </row>
     <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B632" t="inlineStr">
         <is>
           <t>Tempoal</t>
@@ -8735,6 +11735,11 @@
       </c>
     </row>
     <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B633" t="inlineStr">
         <is>
           <t>Teocelo</t>
@@ -8748,6 +11753,11 @@
       </c>
     </row>
     <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B634" t="inlineStr">
         <is>
           <t>Texistepec</t>
@@ -8761,6 +11771,11 @@
       </c>
     </row>
     <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B635" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -8774,6 +11789,11 @@
       </c>
     </row>
     <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B636" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -8787,6 +11807,11 @@
       </c>
     </row>
     <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B637" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -8796,10 +11821,15 @@
         <v>2</v>
       </c>
       <c r="D637">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B638" t="inlineStr">
         <is>
           <t>Tlachichilco</t>
@@ -8809,10 +11839,15 @@
         <v>2</v>
       </c>
       <c r="D638">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B639" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -8826,6 +11861,11 @@
       </c>
     </row>
     <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B640" t="inlineStr">
         <is>
           <t>Tlaltetela</t>
@@ -8835,10 +11875,15 @@
         <v>2</v>
       </c>
       <c r="D640">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B641" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -8852,6 +11897,11 @@
       </c>
     </row>
     <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B642" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -8865,6 +11915,11 @@
       </c>
     </row>
     <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B643" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -8878,6 +11933,11 @@
       </c>
     </row>
     <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B644" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -8891,6 +11951,11 @@
       </c>
     </row>
     <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B645" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -8904,6 +11969,11 @@
       </c>
     </row>
     <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B646" t="inlineStr">
         <is>
           <t>Zentla</t>
@@ -8913,10 +11983,15 @@
         <v>2</v>
       </c>
       <c r="D646">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B647" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -8930,6 +12005,11 @@
       </c>
     </row>
     <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B648" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8961,6 +12041,11 @@
       </c>
     </row>
     <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B650" t="inlineStr">
         <is>
           <t>Tunkás</t>
@@ -8974,6 +12059,11 @@
       </c>
     </row>
     <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B651" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9005,6 +12095,11 @@
       </c>
     </row>
     <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B653" t="inlineStr">
         <is>
           <t>El Salvador</t>
@@ -9014,10 +12109,15 @@
         <v>2</v>
       </c>
       <c r="D653">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B654" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -9031,6 +12131,11 @@
       </c>
     </row>
     <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B655" t="inlineStr">
         <is>
           <t>General Francisco R. Murguía</t>
@@ -9044,6 +12149,11 @@
       </c>
     </row>
     <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B656" t="inlineStr">
         <is>
           <t>General Pánfilo Natera</t>
@@ -9053,10 +12163,15 @@
         <v>2</v>
       </c>
       <c r="D656">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B657" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -9070,6 +12185,11 @@
       </c>
     </row>
     <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B658" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -9083,6 +12203,11 @@
       </c>
     </row>
     <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B659" t="inlineStr">
         <is>
           <t>Juan Aldama</t>
@@ -9096,6 +12221,11 @@
       </c>
     </row>
     <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B660" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -9109,6 +12239,11 @@
       </c>
     </row>
     <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B661" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -9122,6 +12257,11 @@
       </c>
     </row>
     <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B662" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -9135,6 +12275,11 @@
       </c>
     </row>
     <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B663" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -9148,6 +12293,11 @@
       </c>
     </row>
     <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B664" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -9161,6 +12311,11 @@
       </c>
     </row>
     <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B665" t="inlineStr">
         <is>
           <t>Tepechitlán</t>
@@ -9170,10 +12325,15 @@
         <v>2</v>
       </c>
       <c r="D665">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B666" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -9187,6 +12347,11 @@
       </c>
     </row>
     <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B667" t="inlineStr">
         <is>
           <t>Vetagrande</t>
@@ -9196,10 +12361,15 @@
         <v>2</v>
       </c>
       <c r="D667">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B668" t="inlineStr">
         <is>
           <t>Villa González Ortega</t>
@@ -9213,6 +12383,11 @@
       </c>
     </row>
     <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B669" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -9226,6 +12401,11 @@
       </c>
     </row>
     <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B670" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9249,41 +12429,6 @@
       </c>
       <c r="D671">
         <v>1</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
